--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1388</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>15.40887129129672</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>113</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>1.254468628181937</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>59</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.6549880448029585</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>9</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>46</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.5106686451006117</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>655</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>7.271477446541319</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>105</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>1.16565668990357</v>
       </c>
@@ -2245,9 +2215,6 @@
       <c r="O12" t="n">
         <v>35</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.3885522299678568</v>
       </c>
@@ -2393,9 +2360,6 @@
       <c r="O13" t="n">
         <v>10018</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>111.2147497090854</v>
       </c>
@@ -2541,9 +2505,6 @@
       <c r="O14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -2689,9 +2650,6 @@
       <c r="O15" t="n">
         <v>740</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>8.215104290748972</v>
       </c>
@@ -2837,9 +2795,6 @@
       <c r="O16" t="n">
         <v>1131</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>12.55578777410417</v>
       </c>
@@ -2985,9 +2940,6 @@
       <c r="O17" t="n">
         <v>23</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.2553343225503059</v>
       </c>
@@ -3133,9 +3085,6 @@
       <c r="O18" t="n">
         <v>19</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -3281,9 +3230,6 @@
       <c r="O19" t="n">
         <v>135</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>1.498701458447447</v>
       </c>
@@ -3429,9 +3375,6 @@
       <c r="O20" t="n">
         <v>38</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.4218567068222445</v>
       </c>
@@ -3577,9 +3520,6 @@
       <c r="O21" t="n">
         <v>5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -3725,9 +3665,6 @@
       <c r="O22" t="n">
         <v>86</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.954728336492448</v>
       </c>
@@ -3873,9 +3810,6 @@
       <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -4021,9 +3955,6 @@
       <c r="O24" t="n">
         <v>121</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.343280566460305</v>
       </c>
@@ -4169,9 +4100,6 @@
       <c r="O25" t="n">
         <v>97</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>1.076844751625203</v>
       </c>
@@ -4317,9 +4245,6 @@
       <c r="O26" t="n">
         <v>6</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.06660895370877544</v>
       </c>
@@ -4465,9 +4390,6 @@
       <c r="O27" t="n">
         <v>32</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.355247753113469</v>
       </c>
@@ -4861,9 +4783,6 @@
       <c r="O29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -6193,9 +6112,6 @@
       <c r="O38" t="n">
         <v>575</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>6.383358063757647</v>
       </c>
@@ -6341,9 +6257,6 @@
       <c r="O39" t="n">
         <v>7</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -6489,9 +6402,6 @@
       <c r="O40" t="n">
         <v>130</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>1.443193997023468</v>
       </c>
@@ -6637,9 +6547,6 @@
       <c r="O41" t="n">
         <v>76</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.8437134136444889</v>
       </c>
@@ -6785,9 +6692,6 @@
       <c r="O42" t="n">
         <v>13</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.1443193997023468</v>
       </c>
@@ -6933,9 +6837,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7081,9 +6982,6 @@
       <c r="O44" t="n">
         <v>11</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -7229,9 +7127,6 @@
       <c r="O45" t="n">
         <v>44</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.4884656605310199</v>
       </c>
@@ -7377,9 +7272,6 @@
       <c r="O46" t="n">
         <v>519</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>5.761674495809076</v>
       </c>
@@ -7525,9 +7417,6 @@
       <c r="O47" t="n">
         <v>105</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>1.16565668990357</v>
       </c>
@@ -7673,9 +7562,6 @@
       <c r="O48" t="n">
         <v>23</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.2553343225503059</v>
       </c>
@@ -7821,9 +7707,6 @@
       <c r="O49" t="n">
         <v>2762</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>30.66232169060629</v>
       </c>
@@ -7969,9 +7852,6 @@
       <c r="O50" t="n">
         <v>10</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -8117,9 +7997,6 @@
       <c r="O51" t="n">
         <v>439</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>4.873555113025403</v>
       </c>
@@ -8265,9 +8142,6 @@
       <c r="O52" t="n">
         <v>1061</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>11.77868331416846</v>
       </c>
@@ -8413,9 +8287,6 @@
       <c r="O53" t="n">
         <v>13</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.1443193997023468</v>
       </c>
@@ -8561,9 +8432,6 @@
       <c r="O54" t="n">
         <v>15</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.1665223842719386</v>
       </c>
@@ -8709,9 +8577,6 @@
       <c r="O55" t="n">
         <v>126</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>1.398788027884284</v>
       </c>
@@ -8857,9 +8722,6 @@
       <c r="O56" t="n">
         <v>24</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.2664358148351018</v>
       </c>
@@ -9005,9 +8867,6 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.01110149228479591</v>
       </c>
@@ -9153,9 +9012,6 @@
       <c r="O58" t="n">
         <v>131</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>1.454295489308264</v>
       </c>
@@ -9301,9 +9157,6 @@
       <c r="O59" t="n">
         <v>8</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.08881193827836725</v>
       </c>
@@ -9449,9 +9302,6 @@
       <c r="O60" t="n">
         <v>89</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.9880328133468356</v>
       </c>
@@ -9597,9 +9447,6 @@
       <c r="O61" t="n">
         <v>86</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.954728336492448</v>
       </c>
@@ -9745,9 +9592,6 @@
       <c r="O62" t="n">
         <v>5</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -9893,9 +9737,6 @@
       <c r="O63" t="n">
         <v>28</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.3108417839742854</v>
       </c>
@@ -10289,9 +10130,6 @@
       <c r="O65" t="n">
         <v>3</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -11621,9 +11459,6 @@
       <c r="O74" t="n">
         <v>236</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>2.619952179211834</v>
       </c>
@@ -11769,9 +11604,6 @@
       <c r="O75" t="n">
         <v>8</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.08881193827836725</v>
       </c>
@@ -11917,9 +11749,6 @@
       <c r="O76" t="n">
         <v>117</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>1.298874597321121</v>
       </c>
@@ -12065,9 +11894,6 @@
       <c r="O77" t="n">
         <v>66</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.7326984907965298</v>
       </c>
@@ -12213,9 +12039,6 @@
       <c r="O78" t="n">
         <v>15</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.1665223842719386</v>
       </c>
@@ -12361,9 +12184,6 @@
       <c r="O79" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -12509,9 +12329,6 @@
       <c r="O80" t="n">
         <v>12</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.1332179074175509</v>
       </c>
@@ -12657,9 +12474,6 @@
       <c r="O81" t="n">
         <v>42</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.4662626759614281</v>
       </c>
@@ -12805,9 +12619,6 @@
       <c r="O82" t="n">
         <v>543</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>6.028110310644178</v>
       </c>
@@ -12953,9 +12764,6 @@
       <c r="O83" t="n">
         <v>108</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>1.198961166757958</v>
       </c>
@@ -13101,9 +12909,6 @@
       <c r="O84" t="n">
         <v>21</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.2331313379807141</v>
       </c>
@@ -13249,9 +13054,6 @@
       <c r="O85" t="n">
         <v>393</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>4.362886467924791</v>
       </c>
@@ -13397,9 +13199,6 @@
       <c r="O86" t="n">
         <v>10</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -13545,9 +13344,6 @@
       <c r="O87" t="n">
         <v>510</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>5.661761065245912</v>
       </c>
@@ -13693,9 +13489,6 @@
       <c r="O88" t="n">
         <v>1220</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>13.54382058745101</v>
       </c>
@@ -13841,9 +13634,6 @@
       <c r="O89" t="n">
         <v>19</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -13989,9 +13779,6 @@
       <c r="O90" t="n">
         <v>19</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -14137,9 +13924,6 @@
       <c r="O91" t="n">
         <v>106</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>1.176758182188366</v>
       </c>
@@ -14285,9 +14069,6 @@
       <c r="O92" t="n">
         <v>30</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.3330447685438772</v>
       </c>
@@ -14433,9 +14214,6 @@
       <c r="O93" t="n">
         <v>4</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -14581,9 +14359,6 @@
       <c r="O94" t="n">
         <v>261</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>2.897489486331732</v>
       </c>
@@ -14729,9 +14504,6 @@
       <c r="O95" t="n">
         <v>3</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -14877,9 +14649,6 @@
       <c r="O96" t="n">
         <v>120</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>1.332179074175509</v>
       </c>
@@ -15025,9 +14794,6 @@
       <c r="O97" t="n">
         <v>107</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>1.187859674473162</v>
       </c>
@@ -15173,9 +14939,6 @@
       <c r="O98" t="n">
         <v>6</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.06660895370877544</v>
       </c>
@@ -15321,9 +15084,6 @@
       <c r="O99" t="n">
         <v>32</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.355247753113469</v>
       </c>
@@ -15717,9 +15477,6 @@
       <c r="O101" t="n">
         <v>11</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -16161,9 +15918,6 @@
       <c r="O104" t="n">
         <v>44</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.4884656605310199</v>
       </c>
@@ -16309,9 +16063,6 @@
       <c r="O105" t="n">
         <v>103</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>1.143453705333978</v>
       </c>
@@ -16457,9 +16208,6 @@
       <c r="O106" t="n">
         <v>59</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.6549880448029585</v>
       </c>
@@ -16605,9 +16353,6 @@
       <c r="O107" t="n">
         <v>67</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.7437999830813258</v>
       </c>
@@ -16753,9 +16498,6 @@
       <c r="O108" t="n">
         <v>36</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.3996537222526526</v>
       </c>
@@ -16901,9 +16643,6 @@
       <c r="O109" t="n">
         <v>50</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.5550746142397954</v>
       </c>
@@ -17049,9 +16788,6 @@
       <c r="O110" t="n">
         <v>49</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.5439731219549995</v>
       </c>
@@ -17197,9 +16933,6 @@
       <c r="O111" t="n">
         <v>52</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.5772775988093871</v>
       </c>
@@ -17345,9 +17078,6 @@
       <c r="O112" t="n">
         <v>97</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>1.076844751625203</v>
       </c>
@@ -17493,9 +17223,6 @@
       <c r="O113" t="n">
         <v>2</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -17641,9 +17368,6 @@
       <c r="O114" t="n">
         <v>97</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>1.076844751625203</v>
       </c>
@@ -17789,9 +17513,6 @@
       <c r="O115" t="n">
         <v>72</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.7993074445053052</v>
       </c>
@@ -17937,9 +17658,6 @@
       <c r="O116" t="n">
         <v>9</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -18085,9 +17803,6 @@
       <c r="O117" t="n">
         <v>7</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -18233,9 +17948,6 @@
       <c r="O118" t="n">
         <v>14</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -18381,9 +18093,6 @@
       <c r="O119" t="n">
         <v>28</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.3108417839742854</v>
       </c>
@@ -18529,9 +18238,6 @@
       <c r="O120" t="n">
         <v>512</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>5.683964049815504</v>
       </c>
@@ -18677,9 +18383,6 @@
       <c r="O121" t="n">
         <v>89</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.9880328133468356</v>
       </c>
@@ -18825,9 +18528,6 @@
       <c r="O122" t="n">
         <v>17</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -18973,9 +18673,6 @@
       <c r="O123" t="n">
         <v>98</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.087946243909999</v>
       </c>
@@ -19121,9 +18818,6 @@
       <c r="O124" t="n">
         <v>9</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -19269,9 +18963,6 @@
       <c r="O125" t="n">
         <v>563</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>6.250140156340096</v>
       </c>
@@ -19417,9 +19108,6 @@
       <c r="O126" t="n">
         <v>1027</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>11.4012325764854</v>
       </c>
@@ -19565,9 +19253,6 @@
       <c r="O127" t="n">
         <v>14</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -19713,9 +19398,6 @@
       <c r="O128" t="n">
         <v>17</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -19861,9 +19543,6 @@
       <c r="O129" t="n">
         <v>101</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>1.121250720764387</v>
       </c>
@@ -20009,9 +19688,6 @@
       <c r="O130" t="n">
         <v>21</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.2331313379807141</v>
       </c>
@@ -20157,9 +19833,6 @@
       <c r="O131" t="n">
         <v>3</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -20305,9 +19978,6 @@
       <c r="O132" t="n">
         <v>392</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>4.351784975639996</v>
       </c>
@@ -20453,9 +20123,6 @@
       <c r="O133" t="n">
         <v>7</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -20601,9 +20268,6 @@
       <c r="O134" t="n">
         <v>141</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>1.565310412156223</v>
       </c>
@@ -20749,9 +20413,6 @@
       <c r="O135" t="n">
         <v>108</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>1.198961166757958</v>
       </c>
@@ -20897,9 +20558,6 @@
       <c r="O136" t="n">
         <v>10</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -21045,9 +20703,6 @@
       <c r="O137" t="n">
         <v>25</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.2775373071198977</v>
       </c>
@@ -21441,9 +21096,6 @@
       <c r="O139" t="n">
         <v>32</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.355247753113469</v>
       </c>
@@ -21589,9 +21241,6 @@
       <c r="O140" t="n">
         <v>27</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.2997402916894895</v>
       </c>
@@ -21737,9 +21386,6 @@
       <c r="O141" t="n">
         <v>27</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.2997402916894895</v>
       </c>
@@ -21885,9 +21531,6 @@
       <c r="O142" t="n">
         <v>25</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.2775373071198977</v>
       </c>
@@ -22033,9 +21676,6 @@
       <c r="O143" t="n">
         <v>22</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.2442328302655099</v>
       </c>
@@ -22181,9 +21821,6 @@
       <c r="O144" t="n">
         <v>9</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -22329,9 +21966,6 @@
       <c r="O145" t="n">
         <v>14</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -22477,9 +22111,6 @@
       <c r="O146" t="n">
         <v>11</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -22625,9 +22256,6 @@
       <c r="O147" t="n">
         <v>8</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.08881193827836725</v>
       </c>
@@ -22773,9 +22401,6 @@
       <c r="O148" t="n">
         <v>56</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.6216835679485708</v>
       </c>
@@ -22921,9 +22546,6 @@
       <c r="O149" t="n">
         <v>6</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.06660895370877544</v>
       </c>
@@ -23069,9 +22691,6 @@
       <c r="O150" t="n">
         <v>7</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -23217,9 +22836,6 @@
       <c r="O151" t="n">
         <v>5</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -23365,9 +22981,6 @@
       <c r="O152" t="n">
         <v>17</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -23513,9 +23126,6 @@
       <c r="O153" t="n">
         <v>49</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.5439731219549995</v>
       </c>
@@ -23661,9 +23271,6 @@
       <c r="O154" t="n">
         <v>18</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.1998268611263263</v>
       </c>
@@ -23809,9 +23416,6 @@
       <c r="O155" t="n">
         <v>42</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.4662626759614281</v>
       </c>
@@ -23957,9 +23561,6 @@
       <c r="O156" t="n">
         <v>3</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -24105,9 +23706,6 @@
       <c r="O157" t="n">
         <v>851</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>9.447369934361317</v>
       </c>
@@ -24253,9 +23851,6 @@
       <c r="O158" t="n">
         <v>17</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -24401,9 +23996,6 @@
       <c r="O159" t="n">
         <v>18</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.1998268611263263</v>
       </c>
@@ -24549,9 +24141,6 @@
       <c r="O160" t="n">
         <v>68</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.7549014753661216</v>
       </c>
@@ -24697,9 +24286,6 @@
       <c r="O161" t="n">
         <v>44</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.4884656605310199</v>
       </c>
@@ -24845,9 +24431,6 @@
       <c r="O162" t="n">
         <v>2</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -24993,9 +24576,6 @@
       <c r="O163" t="n">
         <v>872</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>9.680501272342031</v>
       </c>
@@ -25141,9 +24721,6 @@
       <c r="O164" t="n">
         <v>11</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -25289,9 +24866,6 @@
       <c r="O165" t="n">
         <v>126</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>1.398788027884284</v>
       </c>
@@ -25437,9 +25011,6 @@
       <c r="O166" t="n">
         <v>132</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>1.46539698159306</v>
       </c>
@@ -25585,9 +25156,6 @@
       <c r="O167" t="n">
         <v>19</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -25733,9 +25301,6 @@
       <c r="O168" t="n">
         <v>68</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.7549014753661216</v>
       </c>
@@ -25881,9 +25446,6 @@
       <c r="O169" t="n">
         <v>14</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -26029,9 +25591,6 @@
       <c r="O170" t="n">
         <v>11</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -26177,9 +25736,6 @@
       <c r="O171" t="n">
         <v>12</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.1332179074175509</v>
       </c>
@@ -26325,9 +25881,6 @@
       <c r="O172" t="n">
         <v>10</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -26473,9 +26026,6 @@
       <c r="O173" t="n">
         <v>17</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -26621,9 +26171,6 @@
       <c r="O174" t="n">
         <v>11</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -26769,9 +26316,6 @@
       <c r="O175" t="n">
         <v>7</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -26917,9 +26461,6 @@
       <c r="O176" t="n">
         <v>7</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -27065,9 +26606,6 @@
       <c r="O177" t="n">
         <v>46</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.5106686451006117</v>
       </c>
@@ -27213,9 +26751,6 @@
       <c r="O178" t="n">
         <v>5</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -27361,9 +26896,6 @@
       <c r="O179" t="n">
         <v>12</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.1332179074175509</v>
       </c>
@@ -27509,9 +27041,6 @@
       <c r="O180" t="n">
         <v>1</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.01110149228479591</v>
       </c>
@@ -27657,9 +27186,6 @@
       <c r="O181" t="n">
         <v>18</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.1998268611263263</v>
       </c>
@@ -27805,9 +27331,6 @@
       <c r="O182" t="n">
         <v>37</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.4107552145374486</v>
       </c>
@@ -27953,9 +27476,6 @@
       <c r="O183" t="n">
         <v>1095</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>12.15613405185152</v>
       </c>
@@ -28101,9 +27621,6 @@
       <c r="O184" t="n">
         <v>14</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -28249,9 +27766,6 @@
       <c r="O185" t="n">
         <v>22</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.2442328302655099</v>
       </c>
@@ -28397,9 +27911,6 @@
       <c r="O186" t="n">
         <v>46</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.5106686451006117</v>
       </c>
@@ -28545,9 +28056,6 @@
       <c r="O187" t="n">
         <v>4</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -28693,9 +28201,6 @@
       <c r="O188" t="n">
         <v>2137</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>23.72388901260885</v>
       </c>
@@ -28841,9 +28346,6 @@
       <c r="O189" t="n">
         <v>14</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -28989,9 +28491,6 @@
       <c r="O190" t="n">
         <v>165</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>1.831746226991325</v>
       </c>
@@ -29137,9 +28636,6 @@
       <c r="O191" t="n">
         <v>154</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>1.70962981185857</v>
       </c>
@@ -29285,9 +28781,6 @@
       <c r="O192" t="n">
         <v>15</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.1665223842719386</v>
       </c>
@@ -29432,9 +28925,6 @@
       </c>
       <c r="O193" t="n">
         <v>107</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>1.187859674473162</v>

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -9442,13 +9442,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O61" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R61" t="n">
-        <v>0.954728336492448</v>
+        <v>0.9658298287772439</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -14354,13 +14354,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O94" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R94" t="n">
-        <v>2.897489486331732</v>
+        <v>2.908590978616528</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O97" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="R97" t="n">
-        <v>1.187859674473162</v>
+        <v>1.210062659042754</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -19973,13 +19973,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O132" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R132" t="n">
-        <v>4.351784975639996</v>
+        <v>4.362886467924791</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -20408,13 +20408,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O135" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="R135" t="n">
-        <v>1.198961166757958</v>
+        <v>1.232265643612346</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -24571,13 +24571,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="O163" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="R163" t="n">
-        <v>9.680501272342031</v>
+        <v>9.702704256911622</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -25006,13 +25006,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O166" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R166" t="n">
-        <v>1.46539698159306</v>
+        <v>1.476498473877856</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -26746,13 +26746,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O178" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R178" t="n">
-        <v>0.05550746142397953</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -27471,13 +27471,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="O183" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="R183" t="n">
-        <v>12.15613405185152</v>
+        <v>12.16723554413631</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -27761,13 +27761,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O185" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R185" t="n">
-        <v>0.2442328302655099</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -28196,13 +28196,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="O188" t="n">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="R188" t="n">
-        <v>23.72388901260885</v>
+        <v>23.79049796631763</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -28486,13 +28486,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="O190" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="R190" t="n">
-        <v>1.831746226991325</v>
+        <v>1.887253688415304</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -28631,13 +28631,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="O191" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="R191" t="n">
-        <v>1.70962981185857</v>
+        <v>1.820644734706529</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -28994,6 +28994,1166 @@
         </is>
       </c>
       <c r="BC193" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>57</v>
+      </c>
+      <c r="O194" t="n">
+        <v>57</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.6327850602333667</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>7</v>
+      </c>
+      <c r="O195" t="n">
+        <v>7</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0.07771044599357135</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
+      <c r="AT195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>6</v>
+      </c>
+      <c r="O196" t="n">
+        <v>6</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0.06660895370877544</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>37</v>
+      </c>
+      <c r="O197" t="n">
+        <v>37</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0.4107552145374486</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>1280</v>
+      </c>
+      <c r="O198" t="n">
+        <v>1280</v>
+      </c>
+      <c r="R198" t="n">
+        <v>14.20991012453876</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
+      <c r="AT198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>22</v>
+      </c>
+      <c r="O199" t="n">
+        <v>22</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0.2442328302655099</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
+      <c r="AT199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>290</v>
+      </c>
+      <c r="O200" t="n">
+        <v>290</v>
+      </c>
+      <c r="R200" t="n">
+        <v>3.219432762590813</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>243</v>
+      </c>
+      <c r="O201" t="n">
+        <v>243</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2.697662625205405</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -29032,7 +30192,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -29115,7 +30275,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -29125,7 +30285,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -29177,7 +30337,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48808</v>
+        <v>50786</v>
       </c>
     </row>
     <row r="16">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -9587,13 +9587,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R62" t="n">
-        <v>0.05550746142397953</v>
+        <v>0.06660895370877544</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -14354,13 +14354,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O94" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R94" t="n">
-        <v>2.908590978616528</v>
+        <v>2.897489486331732</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -14934,13 +14934,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R98" t="n">
-        <v>0.06660895370877544</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19973,13 +19973,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O132" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="R132" t="n">
-        <v>4.362886467924791</v>
+        <v>4.351784975639996</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -20553,13 +20553,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O136" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R136" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.1332179074175509</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -21091,13 +21091,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O139" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R139" t="n">
-        <v>0.355247753113469</v>
+        <v>0.3774507376830608</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24571,13 +24571,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O163" t="n">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="R163" t="n">
-        <v>9.702704256911622</v>
+        <v>9.691602764626827</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -25151,13 +25151,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O167" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R167" t="n">
-        <v>0.2109283534111222</v>
+        <v>0.2220298456959181</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -25296,13 +25296,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O168" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R168" t="n">
-        <v>0.7549014753661216</v>
+        <v>0.7437999830813258</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28196,13 +28196,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>2143</v>
+        <v>2183</v>
       </c>
       <c r="O188" t="n">
-        <v>2143</v>
+        <v>2183</v>
       </c>
       <c r="R188" t="n">
-        <v>23.79049796631763</v>
+        <v>24.23455765770947</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -28776,13 +28776,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O192" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="R192" t="n">
-        <v>0.1665223842719386</v>
+        <v>0.2331313379807141</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -28921,13 +28921,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="O193" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="R193" t="n">
-        <v>1.187859674473162</v>
+        <v>1.365483551029897</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -29907,17 +29907,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -29936,13 +29936,13 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>290</v>
+        <v>1746</v>
       </c>
       <c r="O200" t="n">
-        <v>290</v>
+        <v>1746</v>
       </c>
       <c r="R200" t="n">
-        <v>3.219432762590813</v>
+        <v>19.38320552925365</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -30052,17 +30052,17 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="O201" t="n">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="R201" t="n">
-        <v>2.697662625205405</v>
+        <v>3.219432762590813</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -30154,6 +30154,441 @@
         </is>
       </c>
       <c r="BC201" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>243</v>
+      </c>
+      <c r="O202" t="n">
+        <v>243</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2.697662625205405</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
+      <c r="AT202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>18</v>
+      </c>
+      <c r="O203" t="n">
+        <v>18</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.1998268611263263</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
+      <c r="AT203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>101</v>
+      </c>
+      <c r="O204" t="n">
+        <v>101</v>
+      </c>
+      <c r="R204" t="n">
+        <v>1.121250720764387</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
+      <c r="AT204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -30275,7 +30710,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
@@ -30285,7 +30720,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -30337,7 +30772,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50786</v>
+        <v>52716</v>
       </c>
     </row>
     <row r="16">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O46" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="R46" t="n">
-        <v>5.761674495809076</v>
+        <v>5.75057300352428</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O47" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R47" t="n">
-        <v>1.16565668990357</v>
+        <v>1.154555197618774</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2553343225503059</v>
+        <v>0.2664358148351018</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R59" t="n">
-        <v>0.08881193827836725</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -12759,13 +12759,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O83" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R83" t="n">
-        <v>1.198961166757958</v>
+        <v>1.176758182188366</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -12904,13 +12904,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R84" t="n">
-        <v>0.2331313379807141</v>
+        <v>0.2220298456959181</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -14064,13 +14064,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O92" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R92" t="n">
-        <v>0.3330447685438772</v>
+        <v>0.3441462608286731</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -17508,13 +17508,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O115" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R115" t="n">
-        <v>0.7993074445053052</v>
+        <v>0.7771044599357135</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -17943,13 +17943,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1554208919871427</v>
+        <v>0.1665223842719386</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -18378,13 +18378,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O121" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R121" t="n">
-        <v>0.9880328133468356</v>
+        <v>1.010235797916428</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -22657,17 +22657,17 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -22686,13 +22686,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="O150" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="R150" t="n">
-        <v>0.07771044599357135</v>
+        <v>1.243367135897142</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -22802,17 +22802,17 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -22831,13 +22831,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="R151" t="n">
-        <v>0.05550746142397953</v>
+        <v>0.7882059522205094</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -22947,17 +22947,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -22976,13 +22976,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O152" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1887253688415304</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -23092,22 +23092,22 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -23121,13 +23121,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="O153" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="R153" t="n">
-        <v>0.5439731219549995</v>
+        <v>0.05550746142397953</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -23237,22 +23237,22 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -23266,13 +23266,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O154" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R154" t="n">
-        <v>0.1998268611263263</v>
+        <v>0.1887253688415304</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -23382,22 +23382,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -23411,13 +23411,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O155" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R155" t="n">
-        <v>0.4662626759614281</v>
+        <v>0.5328716296702035</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -23527,22 +23527,22 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -23556,13 +23556,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>3</v>
+        <v>504</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>504</v>
       </c>
       <c r="R156" t="n">
-        <v>0.03330447685438772</v>
+        <v>5.595152111537137</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -23672,17 +23672,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D034</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Syphilis</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>梅毒</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -23701,13 +23701,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>851</v>
+        <v>84</v>
       </c>
       <c r="O157" t="n">
-        <v>851</v>
+        <v>84</v>
       </c>
       <c r="R157" t="n">
-        <v>9.447369934361317</v>
+        <v>0.9325253519228562</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -23817,22 +23817,22 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -23846,13 +23846,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O158" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R158" t="n">
-        <v>0.1887253688415304</v>
+        <v>0.1998268611263263</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -23962,22 +23962,22 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -23991,13 +23991,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="O159" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="R159" t="n">
-        <v>0.1998268611263263</v>
+        <v>0.4662626759614281</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -24107,22 +24107,22 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -24136,13 +24136,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="O160" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="R160" t="n">
-        <v>0.7549014753661216</v>
+        <v>0.03330447685438772</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -24252,17 +24252,17 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -24281,13 +24281,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>44</v>
+        <v>851</v>
       </c>
       <c r="O161" t="n">
-        <v>44</v>
+        <v>851</v>
       </c>
       <c r="R161" t="n">
-        <v>0.4884656605310199</v>
+        <v>9.447369934361317</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -24397,17 +24397,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D094</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Chlamydia trachomatis infection</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>沙眼衣原体感染</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -24426,13 +24426,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>2</v>
+        <v>1007</v>
       </c>
       <c r="O162" t="n">
-        <v>2</v>
+        <v>1007</v>
       </c>
       <c r="R162" t="n">
-        <v>0.02220298456959181</v>
+        <v>11.17920273078948</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -24542,17 +24542,17 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -24571,13 +24571,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>873</v>
+        <v>17</v>
       </c>
       <c r="O163" t="n">
-        <v>873</v>
+        <v>17</v>
       </c>
       <c r="R163" t="n">
-        <v>9.691602764626827</v>
+        <v>0.1887253688415304</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -24687,17 +24687,17 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -24716,13 +24716,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O164" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R164" t="n">
-        <v>0.122116415132755</v>
+        <v>0.1998268611263263</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -24832,17 +24832,17 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -24861,13 +24861,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="O165" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="R165" t="n">
-        <v>1.398788027884284</v>
+        <v>0.7771044599357135</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -24977,17 +24977,17 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -25006,13 +25006,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="O166" t="n">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="R166" t="n">
-        <v>1.476498473877856</v>
+        <v>0.4884656605310199</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -25122,17 +25122,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -25151,13 +25151,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O167" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="R167" t="n">
-        <v>0.2220298456959181</v>
+        <v>0.02220298456959181</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -25267,22 +25267,22 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -25296,13 +25296,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>67</v>
+        <v>873</v>
       </c>
       <c r="O168" t="n">
-        <v>67</v>
+        <v>873</v>
       </c>
       <c r="R168" t="n">
-        <v>0.7437999830813258</v>
+        <v>9.691602764626827</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -25412,27 +25412,27 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -25441,13 +25441,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O169" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R169" t="n">
-        <v>0.1554208919871427</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -25557,27 +25557,27 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -25586,13 +25586,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="O170" t="n">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="R170" t="n">
-        <v>0.122116415132755</v>
+        <v>1.398788027884284</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -25702,27 +25702,27 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -25731,13 +25731,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="O171" t="n">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="R171" t="n">
-        <v>0.1332179074175509</v>
+        <v>1.476498473877856</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -25847,27 +25847,27 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -25876,13 +25876,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O172" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R172" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.2220298456959181</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -25992,17 +25992,17 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -26012,7 +26012,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -26021,41 +26021,55 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O173" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="R173" t="n">
-        <v>0.1887253688415304</v>
+        <v>0.3219432762590813</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -26122,7 +26136,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -26137,17 +26151,17 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -26157,7 +26171,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -26166,41 +26180,130 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="O174" t="n">
-        <v>11</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0.122116415132755</v>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>SRC_CH_FOPH_IDD</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>Human Immunodeficiency Virus (HIV)</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>country:CH:national</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Source-reported HIV diagnoses at any reported stage.</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN174" t="b">
+        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -26282,17 +26385,17 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -26302,7 +26405,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -26311,13 +26414,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="O175" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="R175" t="n">
-        <v>0.07771044599357135</v>
+        <v>0.7437999830813258</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -26427,17 +26530,17 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -26447,7 +26550,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -26456,13 +26559,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O176" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R176" t="n">
-        <v>0.07771044599357135</v>
+        <v>0.1554208919871427</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -26572,17 +26675,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -26592,22 +26695,22 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="O177" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="R177" t="n">
-        <v>0.5106686451006117</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -26717,17 +26820,17 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -26737,22 +26840,22 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O178" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R178" t="n">
-        <v>0.07771044599357135</v>
+        <v>0.1332179074175509</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -26862,17 +26965,17 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -26882,22 +26985,22 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O179" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R179" t="n">
-        <v>0.1332179074175509</v>
+        <v>0.1110149228479591</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -27007,17 +27110,17 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -27027,22 +27130,22 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O180" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R180" t="n">
-        <v>0.01110149228479591</v>
+        <v>0.1887253688415304</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -27152,42 +27255,42 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O181" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R181" t="n">
-        <v>0.1998268611263263</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -27297,17 +27400,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -27317,22 +27420,22 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="O182" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="R182" t="n">
-        <v>0.4107552145374486</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -27442,42 +27545,42 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1096</v>
+        <v>7</v>
       </c>
       <c r="O183" t="n">
-        <v>1096</v>
+        <v>7</v>
       </c>
       <c r="R183" t="n">
-        <v>12.16723554413631</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -27587,22 +27690,22 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -27616,13 +27719,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="O184" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="R184" t="n">
-        <v>0.1554208919871427</v>
+        <v>0.5106686451006117</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -27732,22 +27835,22 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -27761,13 +27864,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O185" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R185" t="n">
-        <v>0.2553343225503059</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -27877,22 +27980,22 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -27906,13 +28009,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="O186" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="R186" t="n">
-        <v>0.5106686451006117</v>
+        <v>0.1332179074175509</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -28022,22 +28125,22 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -28051,13 +28154,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O187" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R187" t="n">
-        <v>0.04440596913918363</v>
+        <v>0.01110149228479591</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -28167,22 +28270,22 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -28196,13 +28299,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>2183</v>
+        <v>10</v>
       </c>
       <c r="O188" t="n">
-        <v>2183</v>
+        <v>10</v>
       </c>
       <c r="R188" t="n">
-        <v>24.23455765770947</v>
+        <v>0.1110149228479591</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -28312,17 +28415,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -28341,13 +28444,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="O189" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="R189" t="n">
-        <v>0.1554208919871427</v>
+        <v>0.5217701373854076</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -28457,22 +28560,22 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -28486,13 +28589,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="O190" t="n">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="R190" t="n">
-        <v>1.887253688415304</v>
+        <v>0.2109283534111222</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -28602,22 +28705,22 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -28631,13 +28734,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="O191" t="n">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="R191" t="n">
-        <v>1.820644734706529</v>
+        <v>0.4107552145374486</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -28747,22 +28850,22 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -28776,13 +28879,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O192" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R192" t="n">
-        <v>0.2331313379807141</v>
+        <v>0.02220298456959181</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -28892,22 +28995,22 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -28921,13 +29024,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>123</v>
+        <v>1096</v>
       </c>
       <c r="O193" t="n">
-        <v>123</v>
+        <v>1096</v>
       </c>
       <c r="R193" t="n">
-        <v>1.365483551029897</v>
+        <v>12.16723554413631</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -29037,42 +29140,42 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N194" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="O194" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="R194" t="n">
-        <v>0.6327850602333667</v>
+        <v>0.1554208919871427</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -29182,42 +29285,42 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N195" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="O195" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="R195" t="n">
-        <v>0.07771044599357135</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -29327,42 +29430,42 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="O196" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="R196" t="n">
-        <v>0.06660895370877544</v>
+        <v>0.5106686451006117</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -29472,42 +29575,42 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N197" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O197" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R197" t="n">
-        <v>0.4107552145374486</v>
+        <v>0.4218567068222445</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -29617,17 +29720,17 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -29637,22 +29740,22 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N198" t="n">
-        <v>1280</v>
+        <v>4</v>
       </c>
       <c r="O198" t="n">
-        <v>1280</v>
+        <v>4</v>
       </c>
       <c r="R198" t="n">
-        <v>14.20991012453876</v>
+        <v>0.04440596913918363</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -29762,17 +29865,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -29782,22 +29885,22 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>22</v>
+        <v>2183</v>
       </c>
       <c r="O199" t="n">
-        <v>22</v>
+        <v>2183</v>
       </c>
       <c r="R199" t="n">
-        <v>0.2442328302655099</v>
+        <v>24.23455765770947</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -29907,17 +30010,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -29927,22 +30030,22 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>1746</v>
+        <v>14</v>
       </c>
       <c r="O200" t="n">
-        <v>1746</v>
+        <v>14</v>
       </c>
       <c r="R200" t="n">
-        <v>19.38320552925365</v>
+        <v>0.1554208919871427</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -30072,22 +30175,22 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N201" t="n">
-        <v>290</v>
+        <v>170</v>
       </c>
       <c r="O201" t="n">
-        <v>290</v>
+        <v>170</v>
       </c>
       <c r="R201" t="n">
-        <v>3.219432762590813</v>
+        <v>1.887253688415304</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -30217,22 +30320,22 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N202" t="n">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="O202" t="n">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="R202" t="n">
-        <v>2.697662625205405</v>
+        <v>1.820644734706529</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -30362,22 +30465,22 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O203" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R203" t="n">
-        <v>0.1998268611263263</v>
+        <v>0.2331313379807141</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -30507,22 +30610,22 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N204" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="O204" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="R204" t="n">
-        <v>1.121250720764387</v>
+        <v>1.365483551029897</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -30589,6 +30692,2471 @@
         </is>
       </c>
       <c r="BC204" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>57</v>
+      </c>
+      <c r="O205" t="n">
+        <v>57</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0.6327850602333667</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>7</v>
+      </c>
+      <c r="O206" t="n">
+        <v>7</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.07771044599357135</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
+      <c r="AT206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>6</v>
+      </c>
+      <c r="O207" t="n">
+        <v>6</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0.06660895370877544</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
+      <c r="AT207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>31</v>
+      </c>
+      <c r="O209" t="n">
+        <v>31</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0.3441462608286731</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>38</v>
+      </c>
+      <c r="O210" t="n">
+        <v>38</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.4218567068222445</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>1280</v>
+      </c>
+      <c r="O211" t="n">
+        <v>1280</v>
+      </c>
+      <c r="R211" t="n">
+        <v>14.20991012453876</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>11</v>
+      </c>
+      <c r="O212" t="n">
+        <v>11</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.122116415132755</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>22</v>
+      </c>
+      <c r="O213" t="n">
+        <v>22</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.2442328302655099</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>23</v>
+      </c>
+      <c r="O214" t="n">
+        <v>23</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.2553343225503059</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>10</v>
+      </c>
+      <c r="O215" t="n">
+        <v>10</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.1110149228479591</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>1746</v>
+      </c>
+      <c r="O216" t="n">
+        <v>1746</v>
+      </c>
+      <c r="R216" t="n">
+        <v>19.38320552925365</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
+      <c r="AT216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>10</v>
+      </c>
+      <c r="O217" t="n">
+        <v>10</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.1110149228479591</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
+      <c r="AT217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>290</v>
+      </c>
+      <c r="O218" t="n">
+        <v>290</v>
+      </c>
+      <c r="R218" t="n">
+        <v>3.219432762590813</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr"/>
+      <c r="AT218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>243</v>
+      </c>
+      <c r="O219" t="n">
+        <v>243</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.697662625205405</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>18</v>
+      </c>
+      <c r="O220" t="n">
+        <v>18</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.1998268611263263</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>101</v>
+      </c>
+      <c r="O221" t="n">
+        <v>101</v>
+      </c>
+      <c r="R221" t="n">
+        <v>1.121250720764387</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr"/>
+      <c r="AT221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -30710,7 +33278,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -30720,7 +33288,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -30740,7 +33308,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -30772,7 +33340,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52716</v>
+        <v>54706</v>
       </c>
     </row>
     <row r="16">
